--- a/onagawa_water_tariff/06_capital_plan_update/09_assumption_switch_cost_calc.xlsx
+++ b/onagawa_water_tariff/06_capital_plan_update/09_assumption_switch_cost_calc.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_建設改良費" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_計算用データ" sheetId="5" state="hidden" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_主要ケース" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_参照元" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -248,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -316,6 +317,9 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -776,7 +780,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>調査票 ／ 調査票＋北上川導水管</t>
+          <t>調査票 ／ 調査票＋量水器費</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -1163,7 +1167,7 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>基準内繰入金は控除、基準外繰入金（赤字補填）は控除しないのが原則。区分が未確定。</t>
+          <t>★基準内繰入金は控除、基準外繰入金（赤字補填）は控除しない。経営戦略報告書案3-8⑹は「国が定める繰出基準以外の繰出金によって収入不足を補填している」と述べ、4-1⑷も繰入金を「現金部分の赤字補填」で算定としているため、全額を基準外とみて控除しないのが本文に整合する。</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1301,7 @@
   </mergeCells>
   <dataValidations count="14">
     <dataValidation sqref="C6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"経営戦略の計画,建設改良費調査票,調査票＋北上川導水管"</formula1>
+      <formula1>"経営戦略の計画,建設改良費調査票,調査票＋量水器費"</formula1>
     </dataValidation>
     <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"35,38,40"</formula1>
@@ -2452,7 +2456,7 @@
       </c>
       <c r="G19" s="27" t="inlineStr">
         <is>
-          <t>差 1,011,000。うち670,000は北上川導水管。</t>
+          <t>差 1,011,000。施設区分別では構造物及び設備▲475,000、送水管▲230,000、配水本管▲200,000、量水器費▲106,000。</t>
         </is>
       </c>
     </row>
@@ -2910,19 +2914,19 @@
       </c>
       <c r="B42" s="29" t="inlineStr">
         <is>
-          <t>北上川導水管</t>
+          <t>量水器費</t>
         </is>
       </c>
       <c r="C42" s="30" t="inlineStr">
         <is>
-          <t>経営戦略にはR9に670,000の計上があるが、調査票にない。</t>
+          <t>経営戦略はR8〜R17で106,000を計上しているが、調査票は委託・工事のみを対象としているため計上されていない。</t>
         </is>
       </c>
       <c r="D42" s="31" t="n"/>
       <c r="E42" s="15" t="n"/>
       <c r="G42" s="32" t="inlineStr">
         <is>
-          <t>中止・繰延・記載漏れのいずれか確認する。</t>
+          <t>量水器の更新費を別途見込む必要があるか確認する。</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3482,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>【調査票＋北上川導水管】</t>
+          <t>【調査票＋量水器費】</t>
         </is>
       </c>
     </row>
@@ -3707,17 +3711,17 @@
     <row r="25">
       <c r="A25" s="33" t="inlineStr">
         <is>
-          <t>北上川導水管（調査票に未計上・復元）</t>
+          <t>量水器費（調査票の対象外・経営戦略から復元）</t>
         </is>
       </c>
       <c r="B25" s="34" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="C25" s="34" t="n">
-        <v>670000</v>
+        <v>20000</v>
       </c>
       <c r="D25" s="34" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="E25" s="34" t="n">
         <v>0</v>
@@ -3726,22 +3730,22 @@
         <v>0</v>
       </c>
       <c r="G25" s="34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H25" s="34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I25" s="34" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="J25" s="34" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="K25" s="34" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="L25" s="35" t="n">
-        <v>670000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="26">
@@ -3751,13 +3755,13 @@
         </is>
       </c>
       <c r="B26" s="36" t="n">
-        <v>565400</v>
+        <v>585400</v>
       </c>
       <c r="C26" s="36" t="n">
-        <v>1539600</v>
+        <v>889600</v>
       </c>
       <c r="D26" s="36" t="n">
-        <v>210000</v>
+        <v>230000</v>
       </c>
       <c r="E26" s="36" t="n">
         <v>320000</v>
@@ -3766,22 +3770,22 @@
         <v>320000</v>
       </c>
       <c r="G26" s="36" t="n">
-        <v>320000</v>
+        <v>321000</v>
       </c>
       <c r="H26" s="36" t="n">
-        <v>160000</v>
+        <v>161000</v>
       </c>
       <c r="I26" s="36" t="n">
-        <v>250000</v>
+        <v>254000</v>
       </c>
       <c r="J26" s="36" t="n">
-        <v>250000</v>
+        <v>270000</v>
       </c>
       <c r="K26" s="36" t="n">
-        <v>250000</v>
+        <v>270000</v>
       </c>
       <c r="L26" s="20" t="n">
-        <v>4185000</v>
+        <v>3621000</v>
       </c>
     </row>
   </sheetData>
@@ -5965,7 +5969,7 @@
     <row r="78">
       <c r="A78" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B78" s="33" t="inlineStr">
@@ -5980,21 +5984,21 @@
         <v>15</v>
       </c>
       <c r="E78" s="34" t="n">
-        <v>332674</v>
+        <v>280389</v>
       </c>
       <c r="F78" s="34" t="n">
         <v>25186</v>
       </c>
       <c r="G78" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|損益計算書ベース|35|15</t>
+          <t>調査票＋量水器費|損益計算書ベース|35|15</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B79" s="33" t="inlineStr">
@@ -6009,21 +6013,21 @@
         <v>20</v>
       </c>
       <c r="E79" s="34" t="n">
-        <v>282384</v>
+        <v>230099</v>
       </c>
       <c r="F79" s="34" t="n">
         <v>25186</v>
       </c>
       <c r="G79" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|損益計算書ベース|35|20</t>
+          <t>調査票＋量水器費|損益計算書ベース|35|20</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B80" s="33" t="inlineStr">
@@ -6038,21 +6042,21 @@
         <v>25</v>
       </c>
       <c r="E80" s="34" t="n">
-        <v>252210</v>
+        <v>199925</v>
       </c>
       <c r="F80" s="34" t="n">
         <v>25186</v>
       </c>
       <c r="G80" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|損益計算書ベース|35|25</t>
+          <t>調査票＋量水器費|損益計算書ベース|35|25</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B81" s="33" t="inlineStr">
@@ -6067,21 +6071,21 @@
         <v>30</v>
       </c>
       <c r="E81" s="34" t="n">
-        <v>232094</v>
+        <v>179809</v>
       </c>
       <c r="F81" s="34" t="n">
         <v>25186</v>
       </c>
       <c r="G81" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|損益計算書ベース|35|30</t>
+          <t>調査票＋量水器費|損益計算書ベース|35|30</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B82" s="33" t="inlineStr">
@@ -6096,21 +6100,21 @@
         <v>38</v>
       </c>
       <c r="E82" s="34" t="n">
-        <v>210920</v>
+        <v>158634</v>
       </c>
       <c r="F82" s="34" t="n">
         <v>25186</v>
       </c>
       <c r="G82" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|損益計算書ベース|35|38</t>
+          <t>調査票＋量水器費|損益計算書ベース|35|38</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B83" s="33" t="inlineStr">
@@ -6125,21 +6129,21 @@
         <v>40</v>
       </c>
       <c r="E83" s="34" t="n">
-        <v>206949</v>
+        <v>154664</v>
       </c>
       <c r="F83" s="34" t="n">
         <v>25186</v>
       </c>
       <c r="G83" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|損益計算書ベース|35|40</t>
+          <t>調査票＋量水器費|損益計算書ベース|35|40</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B84" s="33" t="inlineStr">
@@ -6154,21 +6158,21 @@
         <v>15</v>
       </c>
       <c r="E84" s="34" t="n">
-        <v>322292</v>
+        <v>274134</v>
       </c>
       <c r="F84" s="34" t="n">
         <v>23197</v>
       </c>
       <c r="G84" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|損益計算書ベース|38|15</t>
+          <t>調査票＋量水器費|損益計算書ベース|38|15</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B85" s="33" t="inlineStr">
@@ -6183,21 +6187,21 @@
         <v>20</v>
       </c>
       <c r="E85" s="34" t="n">
-        <v>272002</v>
+        <v>223844</v>
       </c>
       <c r="F85" s="34" t="n">
         <v>23197</v>
       </c>
       <c r="G85" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|損益計算書ベース|38|20</t>
+          <t>調査票＋量水器費|損益計算書ベース|38|20</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B86" s="33" t="inlineStr">
@@ -6212,21 +6216,21 @@
         <v>25</v>
       </c>
       <c r="E86" s="34" t="n">
-        <v>241828</v>
+        <v>193670</v>
       </c>
       <c r="F86" s="34" t="n">
         <v>23197</v>
       </c>
       <c r="G86" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|損益計算書ベース|38|25</t>
+          <t>調査票＋量水器費|損益計算書ベース|38|25</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B87" s="33" t="inlineStr">
@@ -6241,21 +6245,21 @@
         <v>30</v>
       </c>
       <c r="E87" s="34" t="n">
-        <v>221712</v>
+        <v>173554</v>
       </c>
       <c r="F87" s="34" t="n">
         <v>23197</v>
       </c>
       <c r="G87" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|損益計算書ベース|38|30</t>
+          <t>調査票＋量水器費|損益計算書ベース|38|30</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B88" s="33" t="inlineStr">
@@ -6270,21 +6274,21 @@
         <v>38</v>
       </c>
       <c r="E88" s="34" t="n">
-        <v>200537</v>
+        <v>152379</v>
       </c>
       <c r="F88" s="34" t="n">
         <v>23197</v>
       </c>
       <c r="G88" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|損益計算書ベース|38|38</t>
+          <t>調査票＋量水器費|損益計算書ベース|38|38</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B89" s="33" t="inlineStr">
@@ -6299,21 +6303,21 @@
         <v>40</v>
       </c>
       <c r="E89" s="34" t="n">
-        <v>196567</v>
+        <v>148409</v>
       </c>
       <c r="F89" s="34" t="n">
         <v>23197</v>
       </c>
       <c r="G89" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|損益計算書ベース|38|40</t>
+          <t>調査票＋量水器費|損益計算書ベース|38|40</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B90" s="33" t="inlineStr">
@@ -6328,21 +6332,21 @@
         <v>15</v>
       </c>
       <c r="E90" s="34" t="n">
-        <v>316235</v>
+        <v>270485</v>
       </c>
       <c r="F90" s="34" t="n">
         <v>22038</v>
       </c>
       <c r="G90" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|損益計算書ベース|40|15</t>
+          <t>調査票＋量水器費|損益計算書ベース|40|15</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B91" s="33" t="inlineStr">
@@ -6357,21 +6361,21 @@
         <v>20</v>
       </c>
       <c r="E91" s="34" t="n">
-        <v>265945</v>
+        <v>220195</v>
       </c>
       <c r="F91" s="34" t="n">
         <v>22038</v>
       </c>
       <c r="G91" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|損益計算書ベース|40|20</t>
+          <t>調査票＋量水器費|損益計算書ベース|40|20</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B92" s="33" t="inlineStr">
@@ -6386,21 +6390,21 @@
         <v>25</v>
       </c>
       <c r="E92" s="34" t="n">
-        <v>235771</v>
+        <v>190021</v>
       </c>
       <c r="F92" s="34" t="n">
         <v>22038</v>
       </c>
       <c r="G92" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|損益計算書ベース|40|25</t>
+          <t>調査票＋量水器費|損益計算書ベース|40|25</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B93" s="33" t="inlineStr">
@@ -6415,21 +6419,21 @@
         <v>30</v>
       </c>
       <c r="E93" s="34" t="n">
-        <v>215655</v>
+        <v>169905</v>
       </c>
       <c r="F93" s="34" t="n">
         <v>22038</v>
       </c>
       <c r="G93" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|損益計算書ベース|40|30</t>
+          <t>調査票＋量水器費|損益計算書ベース|40|30</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B94" s="33" t="inlineStr">
@@ -6444,21 +6448,21 @@
         <v>38</v>
       </c>
       <c r="E94" s="34" t="n">
-        <v>194480</v>
+        <v>148730</v>
       </c>
       <c r="F94" s="34" t="n">
         <v>22038</v>
       </c>
       <c r="G94" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|損益計算書ベース|40|38</t>
+          <t>調査票＋量水器費|損益計算書ベース|40|38</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B95" s="33" t="inlineStr">
@@ -6473,21 +6477,21 @@
         <v>40</v>
       </c>
       <c r="E95" s="34" t="n">
-        <v>190510</v>
+        <v>144760</v>
       </c>
       <c r="F95" s="34" t="n">
         <v>22038</v>
       </c>
       <c r="G95" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|損益計算書ベース|40|40</t>
+          <t>調査票＋量水器費|損益計算書ベース|40|40</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B96" s="33" t="inlineStr">
@@ -6502,21 +6506,21 @@
         <v>15</v>
       </c>
       <c r="E96" s="34" t="n">
-        <v>307489</v>
+        <v>255203</v>
       </c>
       <c r="F96" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G96" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|固定資産台帳ベース|35|15</t>
+          <t>調査票＋量水器費|固定資産台帳ベース|35|15</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B97" s="33" t="inlineStr">
@@ -6531,21 +6535,21 @@
         <v>20</v>
       </c>
       <c r="E97" s="34" t="n">
-        <v>257199</v>
+        <v>204913</v>
       </c>
       <c r="F97" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G97" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|固定資産台帳ベース|35|20</t>
+          <t>調査票＋量水器費|固定資産台帳ベース|35|20</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B98" s="33" t="inlineStr">
@@ -6560,21 +6564,21 @@
         <v>25</v>
       </c>
       <c r="E98" s="34" t="n">
-        <v>227025</v>
+        <v>174739</v>
       </c>
       <c r="F98" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G98" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|固定資産台帳ベース|35|25</t>
+          <t>調査票＋量水器費|固定資産台帳ベース|35|25</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B99" s="33" t="inlineStr">
@@ -6589,21 +6593,21 @@
         <v>30</v>
       </c>
       <c r="E99" s="34" t="n">
-        <v>206909</v>
+        <v>154623</v>
       </c>
       <c r="F99" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G99" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|固定資産台帳ベース|35|30</t>
+          <t>調査票＋量水器費|固定資産台帳ベース|35|30</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B100" s="33" t="inlineStr">
@@ -6618,21 +6622,21 @@
         <v>38</v>
       </c>
       <c r="E100" s="34" t="n">
-        <v>185734</v>
+        <v>133448</v>
       </c>
       <c r="F100" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G100" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|固定資産台帳ベース|35|38</t>
+          <t>調査票＋量水器費|固定資産台帳ベース|35|38</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B101" s="33" t="inlineStr">
@@ -6647,21 +6651,21 @@
         <v>40</v>
       </c>
       <c r="E101" s="34" t="n">
-        <v>181764</v>
+        <v>129478</v>
       </c>
       <c r="F101" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G101" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|固定資産台帳ベース|35|40</t>
+          <t>調査票＋量水器費|固定資産台帳ベース|35|40</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B102" s="33" t="inlineStr">
@@ -6676,21 +6680,21 @@
         <v>15</v>
       </c>
       <c r="E102" s="34" t="n">
-        <v>299094</v>
+        <v>250936</v>
       </c>
       <c r="F102" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G102" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|固定資産台帳ベース|38|15</t>
+          <t>調査票＋量水器費|固定資産台帳ベース|38|15</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B103" s="33" t="inlineStr">
@@ -6705,21 +6709,21 @@
         <v>20</v>
       </c>
       <c r="E103" s="34" t="n">
-        <v>248804</v>
+        <v>200646</v>
       </c>
       <c r="F103" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G103" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|固定資産台帳ベース|38|20</t>
+          <t>調査票＋量水器費|固定資産台帳ベース|38|20</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B104" s="33" t="inlineStr">
@@ -6734,21 +6738,21 @@
         <v>25</v>
       </c>
       <c r="E104" s="34" t="n">
-        <v>218630</v>
+        <v>170472</v>
       </c>
       <c r="F104" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G104" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|固定資産台帳ベース|38|25</t>
+          <t>調査票＋量水器費|固定資産台帳ベース|38|25</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B105" s="33" t="inlineStr">
@@ -6763,21 +6767,21 @@
         <v>30</v>
       </c>
       <c r="E105" s="34" t="n">
-        <v>198514</v>
+        <v>150356</v>
       </c>
       <c r="F105" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G105" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|固定資産台帳ベース|38|30</t>
+          <t>調査票＋量水器費|固定資産台帳ベース|38|30</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B106" s="33" t="inlineStr">
@@ -6792,21 +6796,21 @@
         <v>38</v>
       </c>
       <c r="E106" s="34" t="n">
-        <v>177339</v>
+        <v>129182</v>
       </c>
       <c r="F106" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G106" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|固定資産台帳ベース|38|38</t>
+          <t>調査票＋量水器費|固定資産台帳ベース|38|38</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B107" s="33" t="inlineStr">
@@ -6821,21 +6825,21 @@
         <v>40</v>
       </c>
       <c r="E107" s="34" t="n">
-        <v>173369</v>
+        <v>125211</v>
       </c>
       <c r="F107" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G107" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|固定資産台帳ベース|38|40</t>
+          <t>調査票＋量水器費|固定資産台帳ベース|38|40</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B108" s="33" t="inlineStr">
@@ -6850,21 +6854,21 @@
         <v>15</v>
       </c>
       <c r="E108" s="34" t="n">
-        <v>294198</v>
+        <v>248448</v>
       </c>
       <c r="F108" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G108" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|固定資産台帳ベース|40|15</t>
+          <t>調査票＋量水器費|固定資産台帳ベース|40|15</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B109" s="33" t="inlineStr">
@@ -6879,21 +6883,21 @@
         <v>20</v>
       </c>
       <c r="E109" s="34" t="n">
-        <v>243908</v>
+        <v>198158</v>
       </c>
       <c r="F109" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G109" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|固定資産台帳ベース|40|20</t>
+          <t>調査票＋量水器費|固定資産台帳ベース|40|20</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B110" s="33" t="inlineStr">
@@ -6908,21 +6912,21 @@
         <v>25</v>
       </c>
       <c r="E110" s="34" t="n">
-        <v>213734</v>
+        <v>167984</v>
       </c>
       <c r="F110" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G110" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|固定資産台帳ベース|40|25</t>
+          <t>調査票＋量水器費|固定資産台帳ベース|40|25</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B111" s="33" t="inlineStr">
@@ -6937,21 +6941,21 @@
         <v>30</v>
       </c>
       <c r="E111" s="34" t="n">
-        <v>193618</v>
+        <v>147868</v>
       </c>
       <c r="F111" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|固定資産台帳ベース|40|30</t>
+          <t>調査票＋量水器費|固定資産台帳ベース|40|30</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B112" s="33" t="inlineStr">
@@ -6966,21 +6970,21 @@
         <v>38</v>
       </c>
       <c r="E112" s="34" t="n">
-        <v>172443</v>
+        <v>126693</v>
       </c>
       <c r="F112" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G112" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|固定資産台帳ベース|40|38</t>
+          <t>調査票＋量水器費|固定資産台帳ベース|40|38</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B113" s="33" t="inlineStr">
@@ -6995,14 +6999,14 @@
         <v>40</v>
       </c>
       <c r="E113" s="34" t="n">
-        <v>168472</v>
+        <v>122722</v>
       </c>
       <c r="F113" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G113" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|固定資産台帳ベース|40|40</t>
+          <t>調査票＋量水器費|固定資産台帳ベース|40|40</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8197,7 @@
     <row r="162">
       <c r="A162" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B162" s="33" t="n">
@@ -8205,21 +8209,21 @@
         </is>
       </c>
       <c r="D162" s="34" t="n">
-        <v>88796</v>
+        <v>62682</v>
       </c>
       <c r="E162" s="34" t="n">
-        <v>76388</v>
+        <v>53975</v>
       </c>
       <c r="G162" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.0|経営戦略方式（40年・据置なし）</t>
+          <t>調査票＋量水器費|2.0|経営戦略方式（40年・据置なし）</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B163" s="33" t="n">
@@ -8231,21 +8235,21 @@
         </is>
       </c>
       <c r="D163" s="34" t="n">
-        <v>90374</v>
+        <v>63824</v>
       </c>
       <c r="E163" s="34" t="n">
-        <v>6296</v>
+        <v>6627</v>
       </c>
       <c r="G163" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.0|調査票方式（25/40年・据置3年）</t>
+          <t>調査票＋量水器費|2.0|調査票方式（25/40年・据置3年）</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B164" s="33" t="n">
@@ -8257,21 +8261,21 @@
         </is>
       </c>
       <c r="D164" s="34" t="n">
-        <v>93271</v>
+        <v>65841</v>
       </c>
       <c r="E164" s="34" t="n">
-        <v>74824</v>
+        <v>52871</v>
       </c>
       <c r="G164" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.1|経営戦略方式（40年・据置なし）</t>
+          <t>調査票＋量水器費|2.1|経営戦略方式（40年・据置なし）</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B165" s="33" t="n">
@@ -8283,21 +8287,21 @@
         </is>
       </c>
       <c r="D165" s="34" t="n">
-        <v>94893</v>
+        <v>67015</v>
       </c>
       <c r="E165" s="34" t="n">
-        <v>6188</v>
+        <v>6512</v>
       </c>
       <c r="G165" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.1|調査票方式（25/40年・据置3年）</t>
+          <t>調査票＋量水器費|2.1|調査票方式（25/40年・据置3年）</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B166" s="33" t="n">
@@ -8309,21 +8313,21 @@
         </is>
       </c>
       <c r="D166" s="34" t="n">
-        <v>97748</v>
+        <v>69003</v>
       </c>
       <c r="E166" s="34" t="n">
-        <v>73285</v>
+        <v>51785</v>
       </c>
       <c r="G166" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.2|経営戦略方式（40年・据置なし）</t>
+          <t>調査票＋量水器費|2.2|経営戦略方式（40年・据置なし）</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B167" s="33" t="n">
@@ -8335,21 +8339,21 @@
         </is>
       </c>
       <c r="D167" s="34" t="n">
-        <v>99411</v>
+        <v>70206</v>
       </c>
       <c r="E167" s="34" t="n">
-        <v>6082</v>
+        <v>6399</v>
       </c>
       <c r="G167" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.2|調査票方式（25/40年・据置3年）</t>
+          <t>調査票＋量水器費|2.2|調査票方式（25/40年・据置3年）</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B168" s="33" t="n">
@@ -8361,21 +8365,21 @@
         </is>
       </c>
       <c r="D168" s="34" t="n">
-        <v>102229</v>
+        <v>72166</v>
       </c>
       <c r="E168" s="34" t="n">
-        <v>71769</v>
+        <v>50715</v>
       </c>
       <c r="G168" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.3|経営戦略方式（40年・据置なし）</t>
+          <t>調査票＋量水器費|2.3|経営戦略方式（40年・据置なし）</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B169" s="33" t="n">
@@ -8387,21 +8391,21 @@
         </is>
       </c>
       <c r="D169" s="34" t="n">
-        <v>103930</v>
+        <v>73398</v>
       </c>
       <c r="E169" s="34" t="n">
-        <v>5977</v>
+        <v>6287</v>
       </c>
       <c r="G169" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.3|調査票方式（25/40年・据置3年）</t>
+          <t>調査票＋量水器費|2.3|調査票方式（25/40年・据置3年）</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B170" s="33" t="n">
@@ -8413,21 +8417,21 @@
         </is>
       </c>
       <c r="D170" s="34" t="n">
-        <v>106711</v>
+        <v>75331</v>
       </c>
       <c r="E170" s="34" t="n">
-        <v>70278</v>
+        <v>49663</v>
       </c>
       <c r="G170" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.4|経営戦略方式（40年・据置なし）</t>
+          <t>調査票＋量水器費|2.4|経営戦略方式（40年・据置なし）</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B171" s="33" t="n">
@@ -8439,21 +8443,21 @@
         </is>
       </c>
       <c r="D171" s="34" t="n">
-        <v>108449</v>
+        <v>76589</v>
       </c>
       <c r="E171" s="34" t="n">
-        <v>5873</v>
+        <v>6177</v>
       </c>
       <c r="G171" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.4|調査票方式（25/40年・据置3年）</t>
+          <t>調査票＋量水器費|2.4|調査票方式（25/40年・据置3年）</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B172" s="33" t="n">
@@ -8465,21 +8469,21 @@
         </is>
       </c>
       <c r="D172" s="34" t="n">
-        <v>111196</v>
+        <v>78498</v>
       </c>
       <c r="E172" s="34" t="n">
-        <v>68812</v>
+        <v>48628</v>
       </c>
       <c r="G172" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.5|経営戦略方式（40年・据置なし）</t>
+          <t>調査票＋量水器費|2.5|経営戦略方式（40年・据置なし）</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B173" s="33" t="n">
@@ -8491,21 +8495,21 @@
         </is>
       </c>
       <c r="D173" s="34" t="n">
-        <v>112968</v>
+        <v>79780</v>
       </c>
       <c r="E173" s="34" t="n">
-        <v>5772</v>
+        <v>6068</v>
       </c>
       <c r="G173" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.5|調査票方式（25/40年・据置3年）</t>
+          <t>調査票＋量水器費|2.5|調査票方式（25/40年・据置3年）</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B174" s="33" t="n">
@@ -8517,21 +8521,21 @@
         </is>
       </c>
       <c r="D174" s="34" t="n">
-        <v>115684</v>
+        <v>81666</v>
       </c>
       <c r="E174" s="34" t="n">
-        <v>67369</v>
+        <v>47609</v>
       </c>
       <c r="G174" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.6|経営戦略方式（40年・据置なし）</t>
+          <t>調査票＋量水器費|2.6|経営戦略方式（40年・据置なし）</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B175" s="33" t="n">
@@ -8543,21 +8547,21 @@
         </is>
       </c>
       <c r="D175" s="34" t="n">
-        <v>117486</v>
+        <v>82971</v>
       </c>
       <c r="E175" s="34" t="n">
-        <v>5671</v>
+        <v>5962</v>
       </c>
       <c r="G175" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.6|調査票方式（25/40年・据置3年）</t>
+          <t>調査票＋量水器費|2.6|調査票方式（25/40年・据置3年）</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B176" s="33" t="n">
@@ -8569,21 +8573,21 @@
         </is>
       </c>
       <c r="D176" s="34" t="n">
-        <v>120174</v>
+        <v>84836</v>
       </c>
       <c r="E176" s="34" t="n">
-        <v>65950</v>
+        <v>46608</v>
       </c>
       <c r="G176" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.7|経営戦略方式（40年・据置なし）</t>
+          <t>調査票＋量水器費|2.7|経営戦略方式（40年・据置なし）</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B177" s="33" t="n">
@@ -8595,21 +8599,21 @@
         </is>
       </c>
       <c r="D177" s="34" t="n">
-        <v>122005</v>
+        <v>86162</v>
       </c>
       <c r="E177" s="34" t="n">
-        <v>5573</v>
+        <v>5856</v>
       </c>
       <c r="G177" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.7|調査票方式（25/40年・据置3年）</t>
+          <t>調査票＋量水器費|2.7|調査票方式（25/40年・据置3年）</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B178" s="33" t="n">
@@ -8621,21 +8625,21 @@
         </is>
       </c>
       <c r="D178" s="34" t="n">
-        <v>124666</v>
+        <v>88008</v>
       </c>
       <c r="E178" s="34" t="n">
-        <v>64554</v>
+        <v>45623</v>
       </c>
       <c r="G178" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.8|経営戦略方式（40年・据置なし）</t>
+          <t>調査票＋量水器費|2.8|経営戦略方式（40年・据置なし）</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B179" s="33" t="n">
@@ -8647,21 +8651,21 @@
         </is>
       </c>
       <c r="D179" s="34" t="n">
-        <v>126524</v>
+        <v>89354</v>
       </c>
       <c r="E179" s="34" t="n">
-        <v>5475</v>
+        <v>5753</v>
       </c>
       <c r="G179" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.8|調査票方式（25/40年・据置3年）</t>
+          <t>調査票＋量水器費|2.8|調査票方式（25/40年・据置3年）</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B180" s="33" t="n">
@@ -8673,21 +8677,21 @@
         </is>
       </c>
       <c r="D180" s="34" t="n">
-        <v>129160</v>
+        <v>91182</v>
       </c>
       <c r="E180" s="34" t="n">
-        <v>63182</v>
+        <v>44654</v>
       </c>
       <c r="G180" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.9|経営戦略方式（40年・据置なし）</t>
+          <t>調査票＋量水器費|2.9|経営戦略方式（40年・据置なし）</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B181" s="33" t="n">
@@ -8699,21 +8703,21 @@
         </is>
       </c>
       <c r="D181" s="34" t="n">
-        <v>131042</v>
+        <v>92545</v>
       </c>
       <c r="E181" s="34" t="n">
-        <v>5380</v>
+        <v>5651</v>
       </c>
       <c r="G181" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|2.9|調査票方式（25/40年・据置3年）</t>
+          <t>調査票＋量水器費|2.9|調査票方式（25/40年・据置3年）</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B182" s="33" t="n">
@@ -8725,21 +8729,21 @@
         </is>
       </c>
       <c r="D182" s="34" t="n">
-        <v>133657</v>
+        <v>94357</v>
       </c>
       <c r="E182" s="34" t="n">
-        <v>61833</v>
+        <v>43702</v>
       </c>
       <c r="G182" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|3.0|経営戦略方式（40年・据置なし）</t>
+          <t>調査票＋量水器費|3.0|経営戦略方式（40年・据置なし）</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="33" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管</t>
+          <t>調査票＋量水器費</t>
         </is>
       </c>
       <c r="B183" s="33" t="n">
@@ -8751,14 +8755,14 @@
         </is>
       </c>
       <c r="D183" s="34" t="n">
-        <v>135561</v>
+        <v>95736</v>
       </c>
       <c r="E183" s="34" t="n">
-        <v>5285</v>
+        <v>5550</v>
       </c>
       <c r="G183" s="38" t="inlineStr">
         <is>
-          <t>調査票＋北上川導水管|3.0|調査票方式（25/40年・据置3年）</t>
+          <t>調査票＋量水器費|3.0|調査票方式（25/40年・据置3年）</t>
         </is>
       </c>
     </row>
@@ -8777,7 +8781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8979,40 +8983,40 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>⑤ ④＋控除項目を経営戦略の実額に</t>
+      <c r="B9" s="39" t="inlineStr">
+        <is>
+          <t>⑤ ④＋動力費・薬品費と雑支出を補正（繰入金は控除しない）</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>1060830.7</v>
+        <v>1417690.7</v>
       </c>
       <c r="D9" s="41" t="n">
-        <v>245.8</v>
+        <v>328.5</v>
       </c>
       <c r="E9" s="42" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>93997.10000000001</v>
+        <v>165369.1</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>672327</v>
+        <v>719494</v>
       </c>
       <c r="I9" s="40" t="n">
         <v>1961661.1</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>-1864947.4</v>
+        <v>-1591950.4</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="39" t="inlineStr">
-        <is>
-          <t>⑥ ⑤＋動力費・薬品費と雑支出を補正</t>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>⑥ ⑤＋他会計補助金272,997を控除（基準内とみる場合）</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
@@ -9043,171 +9047,903 @@
     <row r="11">
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>⑦ ⑥＋機械電気を20年償却</t>
+          <t>⑦ ⑤＋他会計補助金＋補助金691,997を控除</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>1216158.4</v>
+        <v>725693.7</v>
       </c>
       <c r="D11" s="41" t="n">
-        <v>281.8</v>
+        <v>168.1</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>125062.7</v>
+        <v>26969.7</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="H11" s="40" t="n">
         <v>719494</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>2033125.8</v>
+        <v>1961661.1</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>-1864947.4</v>
+        <v>-2283947.4</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>⑧ ⑥＋北上川導水管を復元</t>
+          <t>⑧ ⑤＋機械・電気を20年償却</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>1228729.5</v>
+        <v>1489155.4</v>
       </c>
       <c r="D12" s="41" t="n">
-        <v>284.7</v>
+        <v>345</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>127576.9</v>
+        <v>179662.1</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="H12" s="40" t="n">
         <v>719494</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>2014555.8</v>
+        <v>2033125.8</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>-1864947.4</v>
+        <v>-1591950.4</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>⑨ ⑥＋借入利率3.0％</t>
+          <t>⑨ ⑤＋量水器費を戻す</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>1171601.3</v>
+        <v>1426138.8</v>
       </c>
       <c r="D13" s="41" t="n">
-        <v>271.5</v>
+        <v>330.4</v>
       </c>
       <c r="E13" s="42" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>116151.3</v>
+        <v>167058.8</v>
       </c>
       <c r="G13" s="43" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="H13" s="40" t="n">
         <v>719494</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>1961661.1</v>
+        <v>1966397.9</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>-1864947.4</v>
+        <v>-1591950.4</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>⑩ ⑥で減価償却を固定資産台帳ベースに</t>
+          <t>⑩ ⑤＋借入利率3.0％</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>1033873.7</v>
+        <v>1444598.3</v>
       </c>
       <c r="D14" s="41" t="n">
-        <v>239.5</v>
+        <v>334.7</v>
       </c>
       <c r="E14" s="42" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>88605.7</v>
+        <v>170750.7</v>
       </c>
       <c r="G14" s="43" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="H14" s="40" t="n">
         <v>719494</v>
       </c>
       <c r="I14" s="40" t="n">
+        <v>1961661.1</v>
+      </c>
+      <c r="J14" s="40" t="n">
+        <v>-1591950.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>⑪ ⑤で減価償却を固定資産台帳ベースに</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="n">
+        <v>1306870.7</v>
+      </c>
+      <c r="D15" s="41" t="n">
+        <v>302.8</v>
+      </c>
+      <c r="E15" s="42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F15" s="40" t="n">
+        <v>143205.1</v>
+      </c>
+      <c r="G15" s="43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H15" s="40" t="n">
+        <v>719494</v>
+      </c>
+      <c r="I15" s="40" t="n">
         <v>285384.7</v>
       </c>
-      <c r="J14" s="40" t="n">
-        <v>-299491</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="44" t="inlineStr">
+      <c r="J15" s="40" t="n">
+        <v>-26494</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>▼ 読み取り方</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>・①と②の差が、経営戦略と成果品の前提の違いによるものです。建設改良費の改定より、控除項目の扱いの方が影響が大きくなっています。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>・②→④で給水原価が大きく下がるのは、長期前受金戻入益を推計値450,000千円から実額1,542,259千円に置き換えたためです。</t>
+          <t>・①と②の差が、経営戦略と成果品の前提の違いによるものです。建設改良費の改定より、控除項目の扱いの方が影響が大きくなっています。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>・⑩は減価償却費を経営戦略と同じ固定資産台帳ベースに揃えたもので、①に近づきます。</t>
+          <t>・②→④で給水原価が大きく下がるのは、長期前受金戻入益を推計値450,000千円から実額1,542,259千円に置き換えたためです。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>・⑦⑧⑨は、確定していない前提（機械電気の耐用年数・北上川導水管・借入利率）が振れた場合の幅を示しています。</t>
+          <t>・⑤は繰入金を控除しない前提です。経営戦略報告書案が「繰出基準以外の繰出金で補填している」と述べているためで、基準内と認められる分があれば⑥⑦の水準まで下がります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>・⑪は減価償却費を経営戦略と同じ固定資産台帳ベースに揃えたもので、①に近づきます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>・⑧⑨⑩は、確定していない前提（機械電気の耐用年数・量水器費・借入利率）が振れた場合の幅を示しています。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B19:J19"/>
     <mergeCell ref="B20:J20"/>
+    <mergeCell ref="B22:J22"/>
     <mergeCell ref="B17:J17"/>
     <mergeCell ref="B18:J18"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="B16:J16"/>
+    <mergeCell ref="B21:J21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>主要な数値の参照元</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>各数値がどのファイル・シート・行から来ているかの対応表です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>【A】控除項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>参照元</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>確認結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>長期前受金戻入益（既往資産分）</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>経営戦略試算シート【成行】財政シミュ r17</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr">
+        <is>
+          <t>R8 329,946／R9 324,870／R10 311,865／R11 299,986／R12 290,154（5年計1,542,259）</t>
+        </is>
+      </c>
+      <c r="G6" s="30" t="inlineStr">
+        <is>
+          <t>全年度が直接入力の固定値。根拠欄は「固定資産台帳データに基づく算定額」。固定資産台帳そのものは同ブックに含まれていない。実績（【PL】決算数値入力 r26）はR3 336,382／R4 419,320／R5 336,409で、見込額はこの水準と整合している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>長期前受金戻入益（新規取得分）</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>【成行】財政シミュ r18 ＝ 新規取得!P5</t>
+        </is>
+      </c>
+      <c r="D7" s="30" t="inlineStr">
+        <is>
+          <t>R8 0／R9 1,667／R10 2,982／R11 4,298／R12 5,614</t>
+        </is>
+      </c>
+      <c r="G7" s="30" t="inlineStr">
+        <is>
+          <t>国庫補助金を38年で収益化。新規取得シートH3の式は 財政シミュ!$V$77/38。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>成果品の推計値</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>01_rate_reform_simulation_MAIN.xlsx 02_総括原価 C13:G13</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>R8 ▲94,000／R9 ▲92,000／R10 ▲90,000／R11 ▲88,000／R12 ▲86,000（5年計450,000）</t>
+        </is>
+      </c>
+      <c r="G8" s="30" t="inlineStr">
+        <is>
+          <t>注記は「（推計）非キャッシュ控除。減価償却費の約22%を相殺」。経営戦略の見込額はR8で減価償却費の83%、5年平均で77%にあたり、推計値は約3.4分の1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>他会計補助金（収益的収入）</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>【成行】財政シミュ r13 ＝ r44＋r59</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>R8 38,617／R9 47,830／R10 55,812／R11 63,330／R12 67,408（5年計272,997）</t>
+        </is>
+      </c>
+      <c r="G9" s="30" t="inlineStr">
+        <is>
+          <t>総係費の人件費（r44）と支払利息（r59）の合計。根拠欄は「現状の算定式（＝減価償却費＋人件費＋支払利息）」と書かれているが、式に減価償却費は入っていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>補助金（収益的収入）</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>【成行】財政シミュ r14</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>R8 59,000／R9〜R12 各90,000（5年計419,000）</t>
+        </is>
+      </c>
+      <c r="G10" s="30" t="inlineStr">
+        <is>
+          <t>直接入力の固定値で根拠欄なし。料金改定後シートでは同じ行が「既往債の支払利息（r60）」に置き換わっており、2つのシートで中身が食い違っている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>他会計補助金（資本的収入）</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>【成行】財政シミュ r76</t>
+        </is>
+      </c>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>R8〜R17 各3,000</t>
+        </is>
+      </c>
+      <c r="G11" s="30" t="inlineStr">
+        <is>
+          <t>直接入力の固定値。根拠欄は「R6以降はゼロ」とあり、値と矛盾している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>他会計補助（元金償還）</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>【成行】財政シミュ (料金改定後) r79 ＝ r97</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="inlineStr">
+        <is>
+          <t>R8 30,882／R9 44,652／R10 38,509／R11 47,923／R12 53,577</t>
+        </is>
+      </c>
+      <c r="G12" s="30" t="inlineStr">
+        <is>
+          <t>★資本的収入の最下段。R6末の既往債の元金償還額と同額で、企業債元金償還に対する繰出。繰出基準に該当する典型例だが、資本的収支のため収益的収支の総括原価には入らない。成行シートには計上されていない（同じ行は「固定資産売却代金・計上しない」）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>出資金（資本的収入）</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>【成行】財政シミュ r75</t>
+        </is>
+      </c>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>R8 515,000（＝65,000＋450,000）／R9 495,000／R10 60,000／R11 40,000／R12以降 20,000</t>
+        </is>
+      </c>
+      <c r="G13" s="30" t="inlineStr">
+        <is>
+          <t>直接入力の固定値。根拠欄は「予定額」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>【B】経営戦略報告書案の記載</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>箇所</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>記載内容</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>読み取れること</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>3-8 ⑹料金回収率</t>
+        </is>
+      </c>
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>数値が低く、国が定める繰出基準以外の繰出金によって収入不足を補填している状況で、今後も施設更新の予定がありますが、料金改定を行うのか施設更新（投資規模）を先送り又は縮小するのか判断が求められます。</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="G17" s="32" t="inlineStr">
+        <is>
+          <t>現在の繰入金の相当部分が基準外（赤字補填）であると本文が明言している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>4-1 ⑷一般会計繰入金</t>
+        </is>
+      </c>
+      <c r="C18" s="30" t="inlineStr">
+        <is>
+          <t>過去の一般会計からの繰入手法（現金部分の赤字補填）により算定しました。</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="G18" s="32" t="inlineStr">
+        <is>
+          <t>財政シミュの繰入金は赤字補填額として算定されており、繰出基準に基づく積上げではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>4-1 ⑹支払利息</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>企業債残高に地方債の加重平均借入利率（2.1％）を乗じて試算しました。</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="G19" s="32" t="inlineStr">
+        <is>
+          <t>借入利率は2.1％。ただし財政シミュr61の根拠欄には「1.79％」と別の数値が残っている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="29" t="inlineStr">
+        <is>
+          <t>4-1 ⑺企業債償還金</t>
+        </is>
+      </c>
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>建設改良費から補助金収入を控除した残額を企業債で充当し、借入年度の翌年度から40年にわたり元利均等で返済すると仮定して試算しました。</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="G20" s="32" t="inlineStr">
+        <is>
+          <t>据置期間は設定されていない。調査票は据置3年。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>4-5 ⑵②企業債</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>新たに高度処理施設の整備のほか、老朽管布設替えや水道施設耐震化など将来の更新投資に伴い、企業債の元利償還金の額が増加する見込みです。</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="G21" s="32" t="inlineStr">
+        <is>
+          <t>調査票のNo.1〜No.3と対応している。北上川導水管への言及はない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="46" customHeight="1">
+      <c r="A22" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>4-5 ⑵③繰入金</t>
+        </is>
+      </c>
+      <c r="C22" s="30" t="inlineStr">
+        <is>
+          <t>企業債償還及び施設改良費等を水道料金等収入だけで賄うことが困難な状況にあることから、一般会計から一定額を繰入を行う計画となっています。国の定める繰出基準内の繰入金はもとより、不採算地域となる出島地区・江島地区に対する費用負担について、一般会計側との協議を継続していきます。</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="G22" s="32" t="inlineStr">
+        <is>
+          <t>基準内繰入は既にあり、それに加えて離島分の基準外繰入を求めていく方針。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="46" customHeight="1">
+      <c r="A23" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>5 ⑶一般会計繰入金</t>
+        </is>
+      </c>
+      <c r="C23" s="30" t="inlineStr">
+        <is>
+          <t>離半島地区での施設整備には、国の定める基準内繰入金のほかに、地域的事情によるものとして基準外繰入金により整備することが必要となるので、一般会計での負担ができないか検討・協議を行っていきます。</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="G23" s="32" t="inlineStr">
+        <is>
+          <t>基準内と基準外を明確に区別して記述している。現時点では基準外の負担は未確定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="46" customHeight="1">
+      <c r="A24" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>2-2 現状</t>
+        </is>
+      </c>
+      <c r="C24" s="30" t="inlineStr">
+        <is>
+          <t>今後は、本町から24km離れた一級河川・北上川（石巻市）からの導水管や東日本大震災後に未更新の管路、施設の更新による災害危機対策が求められています。</t>
+        </is>
+      </c>
+      <c r="D24" s="31" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="G24" s="32" t="inlineStr">
+        <is>
+          <t>★北上川導水管は「求められている課題」として書かれているだけで、投資計画には計上されていない。更新投資額の内訳（r119）の「取・導水管」は全年度ゼロ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>【C】建設改良費の施設区分別対比（R8〜R17・千円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>施設区分</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>経営戦略の計画</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>建設改良費調査票</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>差引</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>対応する事業</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="45" t="inlineStr">
+        <is>
+          <t>取・導水管</t>
+        </is>
+      </c>
+      <c r="C28" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="45" t="inlineStr">
+        <is>
+          <t>送水管</t>
+        </is>
+      </c>
+      <c r="C29" s="46" t="n">
+        <v>400000</v>
+      </c>
+      <c r="D29" s="46" t="n">
+        <v>170000</v>
+      </c>
+      <c r="E29" s="47" t="n">
+        <v>-230000</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>No.4 江島海底送水管本復旧工事</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="45" t="inlineStr">
+        <is>
+          <t>配水本管</t>
+        </is>
+      </c>
+      <c r="C30" s="46" t="n">
+        <v>1380000</v>
+      </c>
+      <c r="D30" s="46" t="n">
+        <v>1180000</v>
+      </c>
+      <c r="E30" s="47" t="n">
+        <v>-200000</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>No.1 老朽管布設替工事</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="45" t="inlineStr">
+        <is>
+          <t>配水支管</t>
+        </is>
+      </c>
+      <c r="C31" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="45" t="inlineStr">
+        <is>
+          <t>構造物及び設備</t>
+        </is>
+      </c>
+      <c r="C32" s="46" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="D32" s="46" t="n">
+        <v>2165000</v>
+      </c>
+      <c r="E32" s="47" t="n">
+        <v>-475000</v>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>No.2 水道施設耐震化（1,277,000）＋No.3 鷲神高度処理（888,000）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="45" t="inlineStr">
+        <is>
+          <t>量水器費</t>
+        </is>
+      </c>
+      <c r="C33" s="46" t="n">
+        <v>106000</v>
+      </c>
+      <c r="D33" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="47" t="n">
+        <v>-106000</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>調査票の対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="n">
+        <v>4526000</v>
+      </c>
+      <c r="D34" s="20" t="n">
+        <v>3515000</v>
+      </c>
+      <c r="E34" s="20" t="n">
+        <v>-1011000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>※ 経営戦略の内訳は【成行】財政シミュ r119〜r124（更新投資額）。量水器費は同 r93。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C24:E24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/onagawa_water_tariff/06_capital_plan_update/09_assumption_switch_cost_calc.xlsx
+++ b/onagawa_water_tariff/06_capital_plan_update/09_assumption_switch_cost_calc.xlsx
@@ -1157,7 +1157,7 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>他会計補助金 272,997千円</t>
+          <t>控除していない</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>★基準内繰入金は控除、基準外繰入金（赤字補填）は控除しない。経営戦略報告書案3-8⑹は「国が定める繰出基準以外の繰出金によって収入不足を補填している」と述べ、4-1⑷も繰入金を「現金部分の赤字補填」で算定としているため、全額を基準外とみて控除しないのが本文に整合する。</t>
+          <t>★経営戦略の原価計算表（分解原価集計）は他会計補助金を控除していない。期間原価集計J列の控除項目の●印は要領上の分類として付されているだけで、最終集計には反映されていない。これに合わせて控除しないのが確定した前提。繰出基準の整理が変わる場合はここを切り替える。</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
+          <t>控除していない</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
           <t>控除する（26,494千円）</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>控除しない</t>
-        </is>
-      </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>算定要領では営業外収益として控除対象。成果品では控除されていない。</t>
+          <t>期間原価集計では控除項目の●が付いているが、分解原価集計では控除されていない。経営戦略に合わせて控除しない。</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>算入する（36,696千円）／ 算入しない</t>
+          <t>算入する（36,696千円）</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>営業外費用。経営戦略の料金算定でも成果品でも算入されていない。</t>
+          <t>期間原価集計では固定費の●が付いているが、分解原価集計では算入されていない。経営戦略に合わせて算入しない。</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8985,20 +8985,20 @@
     <row r="9">
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t>⑤ ④＋動力費・薬品費と雑支出を補正（繰入金は控除しない）</t>
+          <t>⑤ ④＋動力費・薬品費を補正【確定した前提】</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>1417690.7</v>
+        <v>1407488.7</v>
       </c>
       <c r="D9" s="41" t="n">
-        <v>328.5</v>
+        <v>326.1</v>
       </c>
       <c r="E9" s="42" t="n">
         <v>0.4</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>165369.1</v>
+        <v>163328.7</v>
       </c>
       <c r="G9" s="43" t="n">
         <v>2.4</v>
@@ -9010,26 +9010,26 @@
         <v>1961661.1</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>-1591950.4</v>
+        <v>-1565456.4</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>⑥ ⑤＋他会計補助金272,997を控除（基準内とみる場合）</t>
+          <t>⑥ ⑤＋他会計補助金272,997を控除（繰出基準が変わる場合）</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>1144693.7</v>
+        <v>1134491.7</v>
       </c>
       <c r="D10" s="41" t="n">
-        <v>265.2</v>
+        <v>262.9</v>
       </c>
       <c r="E10" s="42" t="n">
         <v>0.5</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>110769.7</v>
+        <v>108729.3</v>
       </c>
       <c r="G10" s="43" t="n">
         <v>1.9</v>
@@ -9041,7 +9041,7 @@
         <v>1961661.1</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>-1864947.4</v>
+        <v>-1838453.4</v>
       </c>
     </row>
     <row r="11">
@@ -9051,16 +9051,16 @@
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>725693.7</v>
+        <v>715491.7</v>
       </c>
       <c r="D11" s="41" t="n">
-        <v>168.1</v>
+        <v>165.8</v>
       </c>
       <c r="E11" s="42" t="n">
         <v>0.8</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>26969.7</v>
+        <v>24929.3</v>
       </c>
       <c r="G11" s="43" t="n">
         <v>1.2</v>
@@ -9072,7 +9072,7 @@
         <v>1961661.1</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>-2283947.4</v>
+        <v>-2257453.4</v>
       </c>
     </row>
     <row r="12">
@@ -9082,16 +9082,16 @@
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>1489155.4</v>
+        <v>1478953.4</v>
       </c>
       <c r="D12" s="41" t="n">
-        <v>345</v>
+        <v>342.7</v>
       </c>
       <c r="E12" s="42" t="n">
         <v>0.4</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>179662.1</v>
+        <v>177621.7</v>
       </c>
       <c r="G12" s="43" t="n">
         <v>2.5</v>
@@ -9103,7 +9103,7 @@
         <v>2033125.8</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>-1591950.4</v>
+        <v>-1565456.4</v>
       </c>
     </row>
     <row r="13">
@@ -9113,16 +9113,16 @@
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>1426138.8</v>
+        <v>1415936.8</v>
       </c>
       <c r="D13" s="41" t="n">
-        <v>330.4</v>
+        <v>328.1</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>0.4</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>167058.8</v>
+        <v>165018.4</v>
       </c>
       <c r="G13" s="43" t="n">
         <v>2.4</v>
@@ -9134,7 +9134,7 @@
         <v>1966397.9</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>-1591950.4</v>
+        <v>-1565456.4</v>
       </c>
     </row>
     <row r="14">
@@ -9144,16 +9144,16 @@
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>1444598.3</v>
+        <v>1434396.3</v>
       </c>
       <c r="D14" s="41" t="n">
-        <v>334.7</v>
+        <v>332.3</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>0.4</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>170750.7</v>
+        <v>168710.3</v>
       </c>
       <c r="G14" s="43" t="n">
         <v>2.4</v>
@@ -9165,7 +9165,7 @@
         <v>1961661.1</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>-1591950.4</v>
+        <v>-1565456.4</v>
       </c>
     </row>
     <row r="15">
@@ -9175,16 +9175,16 @@
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>1306870.7</v>
+        <v>1296668.7</v>
       </c>
       <c r="D15" s="41" t="n">
-        <v>302.8</v>
+        <v>300.4</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>0.4</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>143205.1</v>
+        <v>141164.7</v>
       </c>
       <c r="G15" s="43" t="n">
         <v>2.2</v>
@@ -9196,46 +9196,77 @@
         <v>285384.7</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>-26494</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="44" t="inlineStr">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>⑫ ⑤＋その他営業収益等を控除し雑支出を算入</t>
+        </is>
+      </c>
+      <c r="C16" s="40" t="n">
+        <v>1417690.7</v>
+      </c>
+      <c r="D16" s="41" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="E16" s="42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F16" s="40" t="n">
+        <v>165369.1</v>
+      </c>
+      <c r="G16" s="43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H16" s="40" t="n">
+        <v>719494</v>
+      </c>
+      <c r="I16" s="40" t="n">
+        <v>1961661.1</v>
+      </c>
+      <c r="J16" s="40" t="n">
+        <v>-1591950.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="44" t="inlineStr">
         <is>
           <t>▼ 読み取り方</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>・①と②の差が、経営戦略と成果品の前提の違いによるものです。建設改良費の改定より、控除項目の扱いの方が影響が大きくなっています。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>・②→④で給水原価が大きく下がるのは、長期前受金戻入益を推計値450,000千円から実額1,542,259千円に置き換えたためです。</t>
+          <t>・①と②の差が、経営戦略と成果品の前提の違いによるものです。建設改良費の改定より、控除項目の扱いの方が影響が大きくなっています。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>・⑤は繰入金を控除しない前提です。経営戦略報告書案が「繰出基準以外の繰出金で補填している」と述べているためで、基準内と認められる分があれば⑥⑦の水準まで下がります。</t>
+          <t>・②→④で給水原価が大きく下がるのは、長期前受金戻入益を推計値450,000千円から実額1,542,259千円に置き換えたためです。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>・⑪は減価償却費を経営戦略と同じ固定資産台帳ベースに揃えたもので、①に近づきます。</t>
+          <t>・⑤は繰入金を控除しない前提です。経営戦略報告書案が「繰出基準以外の繰出金で補填している」と述べているためで、基準内と認められる分があれば⑥⑦の水準まで下がります。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>・⑪は減価償却費を経営戦略と同じ固定資産台帳ベースに揃えたもので、①に近づきます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>・⑧⑨⑩は、確定していない前提（機械電気の耐用年数・量水器費・借入利率）が振れた場合の幅を示しています。</t>
         </is>
@@ -9247,7 +9278,7 @@
     <mergeCell ref="B19:J19"/>
     <mergeCell ref="B20:J20"/>
     <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="B23:J23"/>
     <mergeCell ref="B18:J18"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="B21:J21"/>
@@ -9262,7 +9293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9728,7 +9759,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>【C】建設改良費の施設区分別対比（R8〜R17・千円）</t>
+          <t>【C】経営戦略の原価計算表の作り（【料金算定】分解原価集計）</t>
         </is>
       </c>
     </row>
@@ -9736,214 +9767,474 @@
       <c r="A27" s="5" t="inlineStr"/>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>施設区分</t>
+          <t>費目</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>経営戦略の計画</t>
+          <t>算定式</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>建設改良費調査票</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>差引</t>
-        </is>
-      </c>
+          <t>4年計（円）</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
       <c r="F27" s="5" t="inlineStr"/>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>対応する事業</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
       <c r="A28" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="45" t="inlineStr">
-        <is>
-          <t>取・導水管</t>
-        </is>
-      </c>
-      <c r="C28" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="12" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+      <c r="B28" s="29" t="inlineStr">
+        <is>
+          <t>維持管理費（原浄水）</t>
+        </is>
+      </c>
+      <c r="C28" s="30" t="inlineStr">
+        <is>
+          <t>期間原価集計!O24−O26−O27</t>
+        </is>
+      </c>
+      <c r="D28" s="30" t="inlineStr">
+        <is>
+          <t>255,240,131</t>
+        </is>
+      </c>
+      <c r="G28" s="30" t="inlineStr">
+        <is>
+          <t>原水及び浄水費から動力費・薬品費を除いた額。動力費・薬品費は変動費として別掲。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
       <c r="A29" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="45" t="inlineStr">
-        <is>
-          <t>送水管</t>
-        </is>
-      </c>
-      <c r="C29" s="46" t="n">
-        <v>400000</v>
-      </c>
-      <c r="D29" s="46" t="n">
-        <v>170000</v>
-      </c>
-      <c r="E29" s="47" t="n">
-        <v>-230000</v>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>No.4 江島海底送水管本復旧工事</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
+      <c r="B29" s="29" t="inlineStr">
+        <is>
+          <t>維持管理費（配給水）</t>
+        </is>
+      </c>
+      <c r="C29" s="30" t="inlineStr">
+        <is>
+          <t>期間原価集計!O32−O34−O35</t>
+        </is>
+      </c>
+      <c r="D29" s="30" t="inlineStr">
+        <is>
+          <t>134,698,869</t>
+        </is>
+      </c>
+      <c r="G29" s="30" t="inlineStr">
+        <is>
+          <t>配水及び給水費から同様に控除。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1">
       <c r="A30" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="45" t="inlineStr">
-        <is>
-          <t>配水本管</t>
-        </is>
-      </c>
-      <c r="C30" s="46" t="n">
-        <v>1380000</v>
-      </c>
-      <c r="D30" s="46" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="E30" s="47" t="n">
-        <v>-200000</v>
-      </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>No.1 老朽管布設替工事</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>維持管理費（その他管理）</t>
+        </is>
+      </c>
+      <c r="C30" s="30" t="inlineStr">
+        <is>
+          <t>期間原価集計!O40</t>
+        </is>
+      </c>
+      <c r="D30" s="30" t="inlineStr">
+        <is>
+          <t>130,727,396</t>
+        </is>
+      </c>
+      <c r="G30" s="30" t="inlineStr">
+        <is>
+          <t>総係費。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
       <c r="A31" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B31" s="45" t="inlineStr">
-        <is>
-          <t>配水支管</t>
-        </is>
-      </c>
-      <c r="C31" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
+      <c r="B31" s="29" t="inlineStr">
+        <is>
+          <t>減価償却費等</t>
+        </is>
+      </c>
+      <c r="C31" s="30" t="inlineStr">
+        <is>
+          <t>固定資産台帳集計結果 T6＋T7＋T8</t>
+        </is>
+      </c>
+      <c r="D31" s="30" t="inlineStr">
+        <is>
+          <t>128,750,077</t>
+        </is>
+      </c>
+      <c r="G31" s="30" t="inlineStr">
+        <is>
+          <t>★取水12,729,056＋浄水16,442,189＋配水99,578,832。損益計算書の減価償却費1,591,381,741ではなく、固定資産台帳の自己財源相当分のみ。補助財源で取得した資産の償却費は原価に入れない設計。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
       <c r="A32" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B32" s="45" t="inlineStr">
-        <is>
-          <t>構造物及び設備</t>
-        </is>
-      </c>
-      <c r="C32" s="46" t="n">
-        <v>2640000</v>
-      </c>
-      <c r="D32" s="46" t="n">
-        <v>2165000</v>
-      </c>
-      <c r="E32" s="47" t="n">
-        <v>-475000</v>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>No.2 水道施設耐震化（1,277,000）＋No.3 鷲神高度処理（888,000）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
+      <c r="B32" s="29" t="inlineStr">
+        <is>
+          <t>支払利息</t>
+        </is>
+      </c>
+      <c r="C32" s="30" t="inlineStr">
+        <is>
+          <t>固定資産台帳集計結果 T19＋T20＋T21</t>
+        </is>
+      </c>
+      <c r="D32" s="30" t="inlineStr">
+        <is>
+          <t>39,061,345</t>
+        </is>
+      </c>
+      <c r="G32" s="30" t="inlineStr">
+        <is>
+          <t>★H30末の既往債分のみ。期間原価集計O58の新規債利息32,793,807は算入されていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="40" customHeight="1">
       <c r="A33" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B33" s="45" t="inlineStr">
+      <c r="B33" s="29" t="inlineStr">
+        <is>
+          <t>資産維持費</t>
+        </is>
+      </c>
+      <c r="C33" s="30" t="inlineStr">
+        <is>
+          <t>【料金算定】資産維持費!C12＋C13</t>
+        </is>
+      </c>
+      <c r="D33" s="30" t="inlineStr">
+        <is>
+          <t>41,705,008</t>
+        </is>
+      </c>
+      <c r="G33" s="30" t="inlineStr">
+        <is>
+          <t>対象資産1,042,625,176×1.0%×4年。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="29" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="C34" s="30" t="inlineStr"/>
+      <c r="D34" s="30" t="inlineStr">
+        <is>
+          <t>734,751,816</t>
+        </is>
+      </c>
+      <c r="G34" s="30" t="inlineStr">
+        <is>
+          <t>料金算定期間はR6〜R9の4年（期間原価集計K4〜N4のラベルはH31・R2・R3・R4のまま）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="26" t="inlineStr">
+        <is>
+          <t>★ 控除項目は一切参照されていない。期間原価集計のJ列「控除項目」に●が付いている</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 その他の営業収益・受取利息・他会計補助金・雑収益・長期前受金戻入益は、分解原価集計の算定式に現れない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 補助財源分は「減価償却費と支払利息を固定資産台帳ベースに絞る」ことで原価から除く設計になっている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="26" t="inlineStr">
+        <is>
+          <t>★ 雑支出（期間原価集計O59・固定費の●あり）も分解原価集計では算入されていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="26" t="inlineStr">
+        <is>
+          <t>★ 期間原価集計の営業外収益の内訳（受取利息＋他会計補助金＋雑収益＋長期前受金戻入益）は、</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 R8で373,468,663円となり、同シートの営業外収益合計432,468,663円と59,000,000円合わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 差額は成行シートの「補助金」で、期間原価集計には行そのものがない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>【D】建設改良費の施設区分別対比（R8〜R17・千円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr"/>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>施設区分</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>経営戦略の計画</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>建設改良費調査票</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>差引</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>対応する事業</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" s="45" t="inlineStr">
+        <is>
+          <t>取・導水管</t>
+        </is>
+      </c>
+      <c r="C46" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" s="45" t="inlineStr">
+        <is>
+          <t>送水管</t>
+        </is>
+      </c>
+      <c r="C47" s="46" t="n">
+        <v>400000</v>
+      </c>
+      <c r="D47" s="46" t="n">
+        <v>170000</v>
+      </c>
+      <c r="E47" s="47" t="n">
+        <v>-230000</v>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>No.4 江島海底送水管本復旧工事</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" s="45" t="inlineStr">
+        <is>
+          <t>配水本管</t>
+        </is>
+      </c>
+      <c r="C48" s="46" t="n">
+        <v>1380000</v>
+      </c>
+      <c r="D48" s="46" t="n">
+        <v>1180000</v>
+      </c>
+      <c r="E48" s="47" t="n">
+        <v>-200000</v>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>No.1 老朽管布設替工事</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" s="45" t="inlineStr">
+        <is>
+          <t>配水支管</t>
+        </is>
+      </c>
+      <c r="C49" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B50" s="45" t="inlineStr">
+        <is>
+          <t>構造物及び設備</t>
+        </is>
+      </c>
+      <c r="C50" s="46" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="D50" s="46" t="n">
+        <v>2165000</v>
+      </c>
+      <c r="E50" s="47" t="n">
+        <v>-475000</v>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>No.2 水道施設耐震化（1,277,000）＋No.3 鷲神高度処理（888,000）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B51" s="45" t="inlineStr">
         <is>
           <t>量水器費</t>
         </is>
       </c>
-      <c r="C33" s="46" t="n">
+      <c r="C51" s="46" t="n">
         <v>106000</v>
       </c>
-      <c r="D33" s="46" t="n">
+      <c r="D51" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="47" t="n">
+      <c r="E51" s="47" t="n">
         <v>-106000</v>
       </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G51" s="12" t="inlineStr">
         <is>
           <t>調査票の対象外</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="19" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="C34" s="20" t="n">
+      <c r="C52" s="20" t="n">
         <v>4526000</v>
       </c>
-      <c r="D34" s="20" t="n">
+      <c r="D52" s="20" t="n">
         <v>3515000</v>
       </c>
-      <c r="E34" s="20" t="n">
+      <c r="E52" s="20" t="n">
         <v>-1011000</v>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="12" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>※ 経営戦略の内訳は【成行】財政シミュ r119〜r124（更新投資額）。量水器費は同 r93。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A4:H4"/>
+  <mergeCells count="22">
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="B40:G40"/>
     <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A15:H15"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="B36:G36"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="B41:G41"/>
     <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="A44:H44"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B39:G39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/onagawa_water_tariff/06_capital_plan_update/09_assumption_switch_cost_calc.xlsx
+++ b/onagawa_water_tariff/06_capital_plan_update/09_assumption_switch_cost_calc.xlsx
@@ -2853,14 +2853,14 @@
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>割合(%)欄に金額444,000が入力されているため、繰入金が約3.9兆円になる。総整備費は正しいままなので気づきにくい。</t>
+          <t>「財源構成割合(%)」欄に金額（企業債444,000・繰入金444,000）が入力されている。単純な割合で出せない事業があるため、入力された金額を正として扱う。ただし様式の財源行の数式が割合前提（整備費×入力値÷100）のままのため、集計表の「財源：繰入金」が約3.9兆円、「財源：その他」が同額のマイナスになる。</t>
         </is>
       </c>
       <c r="D39" s="31" t="n"/>
       <c r="E39" s="15" t="n"/>
       <c r="G39" s="32" t="inlineStr">
         <is>
-          <t>割合欄に50を入力する。</t>
+          <t>当方で入力金額から直接集計する。様式の数式は今後の混乱を避けるため修正しておく。女川町への再提出依頼は不要。</t>
         </is>
       </c>
     </row>
